--- a/src/main/resources/TermsandConditions_Field_Values.xlsx
+++ b/src/main/resources/TermsandConditions_Field_Values.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hema.ananthan\eclipse-workspace\com.ggproduct.automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6882909-6761-4E30-9499-621B9F1908E8}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="40" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6CE3725-73F0-42C8-9ED8-95285EE2FDD6}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{1723DB62-37ED-4AF2-A84E-95702473D7B6}"/>
   </bookViews>
@@ -59,14 +59,14 @@
     <t>TermType__c</t>
   </si>
   <si>
-    <t>AutomationT&amp;C</t>
+    <t>TC-598383</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -81,6 +81,13 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9.8000000000000007"/>
+      <color rgb="FF297BDE"/>
+      <name val="Consolas"/>
+      <family val="3"/>
     </font>
   </fonts>
   <fills count="2">
@@ -104,12 +111,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -452,7 +462,7 @@
       <c r="B2" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="4" t="s">
         <v>9</v>
       </c>
     </row>

--- a/src/main/resources/TermsandConditions_Field_Values.xlsx
+++ b/src/main/resources/TermsandConditions_Field_Values.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22325"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6CE3725-73F0-42C8-9ED8-95285EE2FDD6}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6698B84D-8055-4701-A9F3-43AE21C1DBBD}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{1723DB62-37ED-4AF2-A84E-95702473D7B6}"/>
   </bookViews>
@@ -485,7 +485,7 @@
         <v>5</v>
       </c>
       <c r="C4" s="1">
-        <v>43525</v>
+        <v>43891</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
@@ -496,7 +496,7 @@
         <v>6</v>
       </c>
       <c r="C5" s="2">
-        <v>43616</v>
+        <v>44135</v>
       </c>
     </row>
   </sheetData>

--- a/src/main/resources/TermsandConditions_Field_Values.xlsx
+++ b/src/main/resources/TermsandConditions_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22325"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25330"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\rei proj\product_automation\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6698B84D-8055-4701-A9F3-43AE21C1DBBD}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E22D9F97-2E46-44B0-AFA8-A8BFBD1626CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{1723DB62-37ED-4AF2-A84E-95702473D7B6}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="10920" xr2:uid="{1723DB62-37ED-4AF2-A84E-95702473D7B6}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="12">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -44,29 +44,35 @@
     <t>None</t>
   </si>
   <si>
-    <t>Title__c</t>
-  </si>
-  <si>
-    <t>EffectiveFrom__c</t>
-  </si>
-  <si>
-    <t>EffectiveTill__c</t>
-  </si>
-  <si>
-    <t>Condition</t>
-  </si>
-  <si>
-    <t>TermType__c</t>
-  </si>
-  <si>
-    <t>TC-598383</t>
+    <t>TC</t>
+  </si>
+  <si>
+    <t>Term</t>
+  </si>
+  <si>
+    <t>fieldAutoAddToAward__c</t>
+  </si>
+  <si>
+    <t>checked</t>
+  </si>
+  <si>
+    <t>fieldEffectiveFrom__c</t>
+  </si>
+  <si>
+    <t>fieldEffectiveTill__c</t>
+  </si>
+  <si>
+    <t>fieldTermType__c</t>
+  </si>
+  <si>
+    <t>fieldTitle__c</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -86,6 +92,12 @@
       <b/>
       <sz val="9.8000000000000007"/>
       <color rgb="FF297BDE"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF1B1B1B"/>
       <name val="Consolas"/>
       <family val="3"/>
     </font>
@@ -113,14 +125,14 @@
   </cellStyleXfs>
   <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -436,67 +448,78 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{983D7A93-8DD5-4CF2-A5BD-43A88C865AF9}">
-  <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="17.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="4" t="s">
-        <v>9</v>
-      </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
-      <c r="B3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>7</v>
+      <c r="B3" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
-      <c r="B4" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4" s="1">
-        <v>43891</v>
+      <c r="B4" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="2">
+        <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>3</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" s="2">
+        <v>2200</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="2">
-        <v>44135</v>
+      <c r="C6" t="s">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
